--- a/results/Int All Data -0.5/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_6_permute.xlsx
@@ -440,687 +440,687 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7756532725255763</v>
+        <v>0.7815697029458892</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7787090677513455</v>
+        <v>0.7815080734623444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7685196598052508</v>
+        <v>0.7849131024282017</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7720119972061301</v>
+        <v>0.7849131024282017</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7729313036690086</v>
+        <v>0.7873217880767494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7729313036690086</v>
+        <v>0.7855653477957188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7690383746250873</v>
+        <v>0.7855653477957188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7681190681622088</v>
+        <v>0.7866335921771642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.770460988536916</v>
+        <v>0.7886827725050332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7697317063149678</v>
+        <v>0.7763209252639796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7697317063149678</v>
+        <v>0.7763209252639796</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7663164057685197</v>
+        <v>0.7763209252639796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.765982579399318</v>
+        <v>0.7745850281441308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.762557007272279</v>
+        <v>0.7767831463905666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.761031677554542</v>
+        <v>0.7743179670487694</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7578834381034554</v>
+        <v>0.7736297711491844</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7607029869756359</v>
+        <v>0.7721249845926291</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7599891121245738</v>
+        <v>0.7750112987386499</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7593625457085336</v>
+        <v>0.774800731336538</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7572928222194831</v>
+        <v>0.777101565388882</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7560140104359259</v>
+        <v>0.7740303627922265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7528195488721805</v>
+        <v>0.7740303627922265</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7568306010928962</v>
+        <v>0.7685504745470233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7589003245819467</v>
+        <v>0.7623156251283948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.755428530342249</v>
+        <v>0.7621769587904186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7554901598257939</v>
+        <v>0.7619458482271252</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7524600435515016</v>
+        <v>0.7578937096840461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7499948642097045</v>
+        <v>0.7663112699782242</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7484079050084227</v>
+        <v>0.7678365996959613</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7486801018940794</v>
+        <v>0.7700963474259419</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7486801018940794</v>
+        <v>0.7694338304778339</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7520645876987551</v>
+        <v>0.770686963309914</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.75181293397428</v>
+        <v>0.7688688935453387</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.75181293397428</v>
+        <v>0.7687456345782488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7521056740211184</v>
+        <v>0.7678263281153703</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7474064259008176</v>
+        <v>0.786530876371256</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7504776284974732</v>
+        <v>0.7870495911910925</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7463689962611446</v>
+        <v>0.7835572537902132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7460557130531247</v>
+        <v>0.7826584904885163</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7436521631948725</v>
+        <v>0.7829717736965365</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7431745346973992</v>
+        <v>0.7832028842598299</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7440322116767328</v>
+        <v>0.7772042811947902</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7405809605982169</v>
+        <v>0.7787706972348905</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7405809605982169</v>
+        <v>0.7738660175027734</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7390967172028432</v>
+        <v>0.7872961091252721</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7475091417067259</v>
+        <v>0.7819754303792268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7471958584987057</v>
+        <v>0.7816621471712066</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7468414889683224</v>
+        <v>0.7816621471712066</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7459632688278073</v>
+        <v>0.7688637577550435</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7441451990632318</v>
+        <v>0.7698395579111714</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.746985291096594</v>
+        <v>0.7698395579111714</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7413667365134147</v>
+        <v>0.7612525165372448</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7423065861374748</v>
+        <v>0.7423219935083611</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7419933029294548</v>
+        <v>0.7393483709273183</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7428715230699701</v>
+        <v>0.700362586794856</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7359946998644151</v>
+        <v>0.7174134105756194</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7344899133078598</v>
+        <v>0.7208389827026582</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.73755598011422</v>
+        <v>0.7106187600147911</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7381209170467151</v>
+        <v>0.7001879699248121</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7389529150745717</v>
+        <v>0.6923764328854924</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7383468918197132</v>
+        <v>0.6703695714696577</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7372478326964953</v>
+        <v>0.6231767944451292</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7361385019926867</v>
+        <v>0.6144100004108632</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7345515427914047</v>
+        <v>0.5909137598093595</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7314597970335674</v>
+        <v>0.544748140843913</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7303504663297589</v>
+        <v>0.5191308188504047</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7297855293972637</v>
+        <v>0.5226796499445334</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7280290891162332</v>
+        <v>0.5270450716956325</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7329799909610091</v>
+        <v>0.5270450716956325</v>
       </c>
     </row>
     <row r="71">
@@ -1130,497 +1130,497 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7344026048728378</v>
+        <v>0.5234911048112083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7305764411027569</v>
+        <v>0.5056545051152471</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7274436090225564</v>
+        <v>0.5261103578618678</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7274641521837381</v>
+        <v>0.5259819631044825</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7155234397469082</v>
+        <v>0.5238146595998192</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7089855787008505</v>
+        <v>0.5001078515962036</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7089855787008505</v>
+        <v>0.473124409384116</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7089855787008505</v>
+        <v>0.4744289001191503</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7180297054110687</v>
+        <v>0.4744083569579687</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.71585726611611</v>
+        <v>0.4780907185997781</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7069209910020955</v>
+        <v>0.4798574304613994</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7018673733514114</v>
+        <v>0.4698272320144624</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7079121985291097</v>
+        <v>0.4651844775874111</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7088931344755331</v>
+        <v>0.4584000986071737</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7069312625826862</v>
+        <v>0.4670949915773039</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7069312625826862</v>
+        <v>0.4685381486503143</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7039216894695757</v>
+        <v>0.4754611939685279</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7017903364969802</v>
+        <v>0.4936521631948724</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7021241628661818</v>
+        <v>0.4979970417847899</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7017903364969802</v>
+        <v>0.503389621594971</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6921915444348576</v>
+        <v>0.4950336907843379</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6900139693496035</v>
+        <v>0.4919624881876823</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6897006861415834</v>
+        <v>0.4910020954024405</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7172696084473478</v>
+        <v>0.4911921196433707</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.725286577098484</v>
+        <v>0.4911921196433707</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7218815481326266</v>
+        <v>0.4894973088458852</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7150355396688441</v>
+        <v>0.497211265869592</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7061198077160113</v>
+        <v>0.4978378322856321</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.714557911171371</v>
+        <v>0.4933286084062616</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7307716011339824</v>
+        <v>0.4935032252763055</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7295184683019023</v>
+        <v>0.4950080118328608</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7252660339373023</v>
+        <v>0.4950080118328608</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6920631496774724</v>
+        <v>0.4950080118328608</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6964696577509347</v>
+        <v>0.4950080118328608</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6051553062985332</v>
+        <v>0.501838612925757</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5998294917621924</v>
+        <v>0.5020080940055056</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5998294917621924</v>
+        <v>0.5085048687292001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6009953161592505</v>
+        <v>0.5085048687292001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5839444923784872</v>
+        <v>0.5087976087760385</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5565707301039484</v>
+        <v>0.5074571675089362</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5625231110563294</v>
+        <v>0.5123002177575086</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5625231110563294</v>
+        <v>0.5110573565060191</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.56628250955257</v>
+        <v>0.5104461974608653</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5697286248407905</v>
+        <v>0.512669994658778</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5727741484859691</v>
+        <v>0.5394120547269814</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5729179506142406</v>
+        <v>0.5389703767615761</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5699443280331977</v>
+        <v>0.5419799498746867</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5753728583754468</v>
+        <v>0.5472287275565964</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.570386005998603</v>
+        <v>0.5476395907802293</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5825629647890217</v>
+        <v>0.547762849747319</v>
       </c>
     </row>
     <row r="121">
@@ -1630,123 +1630,123 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5828762479970417</v>
+        <v>0.5590410452360409</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5831895312050618</v>
+        <v>0.5607563991947081</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5828762479970417</v>
+        <v>0.5672120875960392</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5903590944574552</v>
+        <v>0.5678386540120793</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5903796376186368</v>
+        <v>0.5471414191215744</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5851205883561362</v>
+        <v>0.5278873413040799</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5790603558075517</v>
+        <v>0.5277589465466946</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5791373926619828</v>
+        <v>0.5277589465466946</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5879401372283167</v>
+        <v>0.5225358478162619</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5920949915773039</v>
+        <v>0.5231829573934837</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.592408274785324</v>
+        <v>0.523162414232302</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5658716463289371</v>
+        <v>0.5183296355643207</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -1756,101 +1756,101 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5095833846912363</v>
+        <v>0.5450614240519331</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5089979045975594</v>
+        <v>0.5395096347425942</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5057212703890874</v>
+        <v>0.5081813139405892</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5057212703890874</v>
+        <v>0.5075342043633674</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5057212703890874</v>
+        <v>0.5058239861949957</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5045708533629155</v>
+        <v>0.5089311393237191</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5036310037388554</v>
+        <v>0.5077601791363655</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5017307613295534</v>
+        <v>0.5013917991700563</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5022340687785036</v>
+        <v>0.5001232589670899</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5022340687785036</v>
+        <v>0.5001438021282715</v>
       </c>
     </row>
     <row r="144">
@@ -1860,127 +1860,127 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5022340687785036</v>
+        <v>0.5026706109536135</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5026706109536135</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5015972307818727</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5015972307818727</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4996148157278442</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5003081474177247</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4983873618472411</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4983873618472411</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4995583220345947</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4983462755248778</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4994556062286865</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4991423230206664</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5006471095772218</v>
       </c>
     </row>
   </sheetData>
